--- a/www/download/COUNTRY.LTU.zdW16.xlsx
+++ b/www/download/COUNTRY.LTU.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>Lituânia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1.15856482646301</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1.15845485170672</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1.06150597892601</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.885206757426866</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.804164448887702</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.802530182712822</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.796476722649701</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.729865783239543</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.679495666264177</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.717595750309479</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.753373683572918</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.717990884133895</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.777602083821911</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.753055489038766</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.751973350643925</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.399</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1.346</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1.397</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1.427</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.411</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1.418</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.416</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.446</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>1.425</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1.318</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1.245</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>1.252</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.274</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>1.292</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>1.317</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1.124</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1.078</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1.114</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1.134</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1.148</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1.172</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1.173</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.234</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>1.259</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>1.119</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.133</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1.157</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2612.717</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2505.268</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2559.502</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2643.032</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2657.404</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2693.83</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2735.9</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2771.906</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2744.239</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>2441.381</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>2340.933</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>2319.569</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2359.055</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>2372.141</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2406.942</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2079.099</t>
+          <t>2850424481.34571</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1980.797</t>
+          <t>2790570996.66151</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2021.935</t>
+          <t>2829121997.86594</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2056.135</t>
+          <t>2928884921.38315</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2173.845</t>
+          <t>2758641647.65947</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2215.233</t>
+          <t>2823488880.74509</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2210.973</t>
+          <t>2831136064.64511</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2351.82</t>
+          <t>2745034740.61769</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2420.548</t>
+          <t>2845422413.78938</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2150.535</t>
+          <t>2284538387.09381</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2086.026</t>
+          <t>2168725763.82076</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2070.567</t>
+          <t>2311517178.33692</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2094.47</t>
+          <t>2322196796.35386</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2090.673</t>
+          <t>2304569732.99074</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2115.612</t>
+          <t>2645597486.84344</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>739808731.849372</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>740448355.717965</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>797152161.718218</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>882124770.040954</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>814344849.699431</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>833462670.731432</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>938809794.433449</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>896574126.86273</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>950555071.636451</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>758483156.18543</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>628155575.357833</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>697064770.306872</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>685621120.22399</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>752778915.539511</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>812061343.203838</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6786945.74215589</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5975260.6647669</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4971823.16724087</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>4031698.47003262</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>3454854.18790753</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>3042339.2975141</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2640123.51897346</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1995996.17542976</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1684172.54594214</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1850564.49037313</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1640048.84714171</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1413880.23595413</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1504112.35555343</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1365061.00315051</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1414623.60139624</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>15738.8237693022</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>14871.7955284747</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>15037.5186871061</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>17209.5712617974</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>17983.1618856534</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>20100.503909227</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>21329.9085929038</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>23472.7626401161</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>24535.8974515378</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>19256.1778666217</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>20095.1504950655</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>21438.4871400205</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>21300.7160092585</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>20989.0708991549</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>21299.5929451013</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>25857.1690138143</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>24943.5486681463</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>25474.1496912314</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>28711.6879289369</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>29801.7199835197</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>32944.9912729953</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>34907.6518500913</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>37967.3982856051</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>42923.971587214</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>31495.4779700969</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>33033.0388005164</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>37539.5469511819</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>36838.610929183</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>36346.9989142802</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>41871.2543135088</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.81031962788905</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.67513187746815</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.53644799211462</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.33088908715775</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.66944034926033</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.65786708606392</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.35508088337987</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.62311830057982</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1.54645740391753</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.83531016142203</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2.32087476706974</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.970408329614</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2.05485046801905</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.77727358835712</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.60523668280187</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.15856482646301</t>
+          <t>658.391979646309</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.15845485170672</t>
+          <t>686.623907601113</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.06150597892601</t>
+          <t>715.422316303685</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.885206757426866</t>
+          <t>777.832930693561</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.804164448887702</t>
+          <t>709.551228728516</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.802530182712822</t>
+          <t>711.024288288204</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796476722649701</t>
+          <t>800.096980861492</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729865783239543</t>
+          <t>726.535709428163</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679495666264177</t>
+          <t>755.175949882779</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.717595750309479</t>
+          <t>653.983183322351</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.753373683572918</t>
+          <t>566.002807109175</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.717990884133895</t>
+          <t>622.774053468602</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.777602083821911</t>
+          <t>605.233947338491</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.753055489038766</t>
+          <t>660.42507329056</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.751973350643925</t>
+          <t>701.692180182874</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>18769722.8246657</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>83720331.2109546</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>110684262.676931</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>165041591.213746</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>190068864.47185</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>181513190.609971</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>203536504.586254</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>194548609.870288</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>370883946.339109</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>353425511.984608</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>311508190.920801</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>488817828.494084</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>542727214.249834</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>672684854.206051</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>786398223.903079</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6067999.36470752</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>59303332.0438902</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>54364017.8281375</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>102924699.912834</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>121124793.885737</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>90525005.4332718</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>109599505.689512</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>66880787.9340062</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>289917212.29938</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>193225662.588687</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>214432351.089904</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>416095838.637547</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>439799095.894353</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>530259709.446284</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>576783217.8031</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>12701723.4599582</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>24416999.1670644</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>56320244.8487934</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>62116891.3009118</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>68944070.5861129</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>90988185.1766996</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>93936998.8967423</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>127667821.936282</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>80966734.0397292</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>160199849.395922</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>97075839.8308976</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>72721989.8565376</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>102928118.355481</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>142425144.759767</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>209615006.099979</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1850.29190324475</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1836.80950305548</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>1814.63149770247</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>1813.04228978555</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>1894.10467983515</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>1889.80805323324</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>1884.29310447685</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>1905.78911542576</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>1923.02338883946</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>1854.24516507299</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>1879.6244402195</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>1849.89323589061</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>1848.89920728801</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>1834.18111313869</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>1828.07420784764</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1867.57383022897</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1861.15815851263</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1831.70914804668</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1851.86137129545</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1883.18808741747</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>1900.0203085673</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>1931.90058395534</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>1917.54434550746</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>1925.6737786759</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>1852.70346441359</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>1879.72389361806</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>1852.7350337419</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>1852.08440904772</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>1835.8800657703</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>1828.09412841999</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>3150.65139588202</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3938.36974205644</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>5040.61573152859</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>6962.28994099796</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>9124.35207412529</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>12049.1761107419</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>14238.3888159332</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>16983.0911769822</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>23559.9165111201</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>16632.3913132201</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>20559.3630151165</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>27620.302820059</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>29388.0928166548</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>32604.8556979083</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>32722.5252886051</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>464016540.436009</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>544482188.424814</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>628548358.760717</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>707070988.71074</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>655755538.460335</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>755396955.001453</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>785441895.905151</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>771096015.430767</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>848657089.501794</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>668564664.67631</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>736763454.249048</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>867478302.369087</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>956705500.109376</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>991719768.889271</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1172377631.81601</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>4719.24602194144</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5450.93145745449</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>6674.78287683247</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>8692.08771253529</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>11133.0465974494</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>13999.6776093669</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>17049.7061842881</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>21098.6625927521</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>27599.4330809008</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>16670.7148694958</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>20546.9280135594</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>27585.0153639521</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>27752.9142861875</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>30547.798611909</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>30442.4767728656</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2612.717</t>
+          <t>697299248.439522</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2505.268</t>
+          <t>843486751.762538</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2559.502</t>
+          <t>973291991.673647</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2643.032</t>
+          <t>1105652173.67365</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2657.404</t>
+          <t>1092941712.51979</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2693.83</t>
+          <t>1154545480.55657</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2735.9</t>
+          <t>1273663194.43856</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2771.906</t>
+          <t>1323005610.62886</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2744.239</t>
+          <t>1525771942.16906</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2441.381</t>
+          <t>1025253493.04811</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2340.933</t>
+          <t>1047327735.24133</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2319.569</t>
+          <t>1353760346.93414</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2359.055</t>
+          <t>1381144730.78181</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2372.141</t>
+          <t>1514114477.79073</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2406.942</t>
+          <t>1793793667.04007</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2079.099</t>
+          <t>-1568.59462605943</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1980.797</t>
+          <t>-1512.56171539805</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2021.935</t>
+          <t>-1634.16714530388</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2056.135</t>
+          <t>-1729.79777153733</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2173.845</t>
+          <t>-2008.6945233241</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2215.233</t>
+          <t>-1950.50149862503</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2210.973</t>
+          <t>-2811.31736835486</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2351.82</t>
+          <t>-4115.57141576986</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2420.548</t>
+          <t>-4039.51656978071</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2150.535</t>
+          <t>-38.323556275706</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2086.026</t>
+          <t>12.4350015570744</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2070.567</t>
+          <t>35.2874561069235</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2094.47</t>
+          <t>1635.17853046734</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2090.673</t>
+          <t>2057.05708599931</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2115.612</t>
+          <t>2280.04851573949</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3239.897</t>
+          <t>-233282708.003513</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3124.066</t>
+          <t>-299004563.337724</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3163.735</t>
+          <t>-344743632.91293</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3265.421</t>
+          <t>-398581184.962909</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3058.904</t>
+          <t>-437186174.059454</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3143.944</t>
+          <t>-399148525.555113</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3157.531</t>
+          <t>-488221298.533408</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>3037.33</t>
+          <t>-551909595.198093</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3163.674</t>
+          <t>-677114852.667271</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2613.786</t>
+          <t>-356688828.371802</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2456.067</t>
+          <t>-310564280.992279</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2612.015</t>
+          <t>-486282044.565054</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2630.328</t>
+          <t>-424439230.672438</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2618.17</t>
+          <t>-522394708.901462</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2645.597</t>
+          <t>-621416035.224061</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>5189.33502906961</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>5513.5275910855</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>6331.53880080762</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>8461.92150623812</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>10574.3939</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>12158.3974464987</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>14124.7205219016</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>18177.9775782753</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>21769.2636317737</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>16219.8670993454</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>16490.3984705787</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>20070.9696</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>19829.786931743</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>21064.519139338</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>21887.9580228399</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1735.005</t>
+          <t>0.123938110921383</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1663.789</t>
+          <t>0.130944383464075</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1670.045</t>
+          <t>0.137706395879898</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1755.552</t>
+          <t>0.142395464484183</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1664.639</t>
+          <t>0.140788494256387</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1722.676</t>
+          <t>0.144050418393093</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1729.932</t>
+          <t>0.135300599542024</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1697.076</t>
+          <t>0.137881298636784</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1626.48</t>
+          <t>0.147796805641405</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1396.755</t>
+          <t>0.128453749405505</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1319.312</t>
+          <t>0.147092028554398</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1320.086</t>
+          <t>0.161784941878048</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1342.734</t>
+          <t>0.167433415213025</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1330.805</t>
+          <t>0.166198233332554</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1345.796</t>
+          <t>0.163895706832029</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>4507.09782753862</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>4631.44073402065</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>5483.71337637463</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>7287.65448879269</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>9092.17999306117</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>10599.0910269806</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>12903.9475467813</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>16893.134966628</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21113.5463021387</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16706.8492317145</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>15205.9775842268</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>17115.9845111989</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>16673.0053321972</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18189.5694129926</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>19257.6554408496</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>847.595</t>
+          <t>5127.06246830205</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>834.18</t>
+          <t>5422.95637429398</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>898.127</t>
+          <t>6318.64607780542</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>989.962</t>
+          <t>8452.11931484176</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>911.935</t>
+          <t>10504.6119598992</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>935.911</t>
+          <t>12191.4529147747</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1051.476</t>
+          <t>14764.5704486455</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>997.946</t>
+          <t>19428.325410536</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1059.732</t>
+          <t>23404.029213334</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>865.654</t>
+          <t>18477.3558919898</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>710.819</t>
+          <t>16674.522472558</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>785.044</t>
+          <t>18859.2807471078</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>772.54</t>
+          <t>18363.0392845664</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>843.691</t>
+          <t>20178.0086426628</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>812.061</t>
+          <t>21331.270938851</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>145.29</t>
+          <t>41361.3510292618</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>137.45</t>
+          <t>41880.8203712866</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>125.13</t>
+          <t>46802.5548466953</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>107.7</t>
+          <t>59302.2589503403</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>138.38</t>
+          <t>71160.8708480923</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>136.69</t>
+          <t>79539.3281152391</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>110.27</t>
+          <t>92566.0323977185</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>135.67</t>
+          <t>118291.893736853</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>128.41</t>
+          <t>133711.292460252</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>148.43</t>
+          <t>120013.070819408</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>193.47</t>
+          <t>113843.017324706</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>163.75</t>
+          <t>125610.666707677</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>171.11</t>
+          <t>121690.25964673</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>131534.430977248</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>160.52</t>
+          <t>136594.727486177</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>7.732</t>
+          <t>7287.23872003667</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>7630.21006099778</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>5.609</t>
+          <t>8202.50251150318</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>4.535</t>
+          <t>9136.82470853588</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3.838</t>
+          <t>9923.11993326489</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>3.386</t>
+          <t>10776.1636068242</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.955</t>
+          <t>12127.4109549335</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.225</t>
+          <t>13602.4894155949</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.881</t>
+          <t>13849.846941909</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.145</t>
+          <t>11727.0445054314</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>10844.5644578035</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.607</t>
+          <t>11147.8727632681</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.709</t>
+          <t>11457.6238400082</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.562</t>
+          <t>11868.2178498196</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>12410.1591772335</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6504.84430024168</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6644.45107219684</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>7230.11353174702</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>7979.8299435475</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>8693.53836947791</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>9523.46545699687</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>10768.2442046422</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>11942.1003537105</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>12546.7207445945</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>10484.0847288169</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>9889.45818730946</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>10173.3179720649</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>10483.6497398189</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>10759.192613146</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>11245.4851718643</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>5126.24771172289</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5484.05820248778</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>6445.01114590965</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>8444.37270819501</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>10018.6318566761</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>11457.6734937057</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>12524.2396806378</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>16310.2399266418</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>19762.101903809</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>15416.1289244214</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>16745.4003550446</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>20321.9144125645</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>20375.0157708118</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>21860.7900508214</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>22387.2894108753</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2079099000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1980797000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2021935000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2056135000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2173845000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2215233000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2210973000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2351820000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2420548000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2150535000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2086026000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2070567000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2094470000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2090673000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2115612000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2612717112.75203</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2505267774.01068</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2559502143.84006</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2643032104.95401</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2657404373.91654</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2693829793.28363</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2735899649.98004</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2771906228.64831</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2744239188.51545</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2441381463.19636</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2340932948.15619</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2319568680.19385</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2359055474.33635</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2372140632.9818</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2406941853.2429</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1735005427.53296</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1663788974.94404</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1670044944.64661</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1755551742.44378</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1664638798.08949</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1722676106.20362</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1729932271.93526</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1697075696.90971</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1626480261.94854</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1396755355.38056</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1319311579.83028</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1320086024.64373</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1342733974.73732</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1330805264.88213</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1345795593.90387</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1398990</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1346080</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1397330</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1427230</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1411120</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1417790</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1416170</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1445550</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1425080</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1317740</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1245360</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1251970</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1273730</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>1292100</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1316640</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1123660</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1078390</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1114240</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1134080</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1147690</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1172200</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1173370</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1234040</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1258720</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1159790</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1109810</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1119290</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1132820</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1139840</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1157290</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2612717112.75203</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2505267774.01068</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2559502143.84006</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2643032104.95401</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2657404373.91654</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2693829793.28363</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2735899649.98004</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2771906228.64831</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2744239188.51545</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2441381463.19636</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>2340932948.15619</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>2319568680.19385</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2359055474.33635</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2372140632.9818</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2406941853.2429</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2079099000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1980797000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2021935000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2056135000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2173845000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2215233000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2210973000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2351820000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2420548000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2150535000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2086026000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2070567000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2094470000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2090673000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2115612000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>19372.3787848133</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20588.3498919947</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>24090.62757454</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>31388.2037276302</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>38656.80469</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>45498.4464263389</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>53332.4778821863</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>68467.0647980007</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>87005.8837681186</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>63960.5735342206</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>65754.9255570678</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>78302.088</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>76309.2426354663</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>82759.8453207151</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>85667.7869697813</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>10253.4912648133</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10906.8243319947</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>12764.04165454</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>16896.7398876302</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>20523.1061</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>23649.8110463389</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>27289.0738021863</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>35737.7431480007</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>43165.8952481186</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>33893.8462942206</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>33420.0419970678</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>39181.5984</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>38738.0931954663</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>42038.7056007151</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>43718.6263603348</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>61378.4833959078</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>61476.2694821428</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>61854.7425768085</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>64341.0749309992</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>67327.9260119131</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>68369.5198770513</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>72907.1910381308</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>77234.2707172934</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>74131.1874691318</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>74416.1526658829</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>74033.388041996</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>74289.8447858544</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>75610.3422315357</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>76770.3354298668</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>78100.7539259496</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
